--- a/xls/square_un_16_tri3_21.xlsx
+++ b/xls/square_un_16_tri3_21.xlsx
@@ -456,12 +456,82 @@
         <v>10</v>
       </c>
     </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>598</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>340</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>485</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19">
+        <v>2676</v>
+      </c>
+      <c r="I19">
+        <v>-0.0001374637284752597</v>
+      </c>
+      <c r="J19">
+        <v>-0.5122504675722445</v>
+      </c>
+      <c r="K19">
+        <v>2.657847606759506</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <v>598</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>340</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>564</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>3138</v>
+      </c>
+      <c r="I20">
+        <v>-4.4695317076209455e-6</v>
+      </c>
+      <c r="J20">
+        <v>-0.009564883447708866</v>
+      </c>
+      <c r="K20">
+        <v>3.2027111743482077</v>
+      </c>
+    </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
         <v>11</v>
       </c>
       <c r="B21">
-        <v>553</v>
+        <v>598</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -473,22 +543,22 @@
         <v>12</v>
       </c>
       <c r="F21">
-        <v>484</v>
+        <v>598</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
       <c r="H21">
-        <v>2646</v>
+        <v>3330</v>
       </c>
       <c r="I21">
-        <v>-2.6410867099967863</v>
+        <v>-1.566336761345978e-7</v>
       </c>
       <c r="J21">
-        <v>-2.1807157033981697</v>
+        <v>-0.0003376943310008203</v>
       </c>
       <c r="K21">
-        <v>0.31411608973650373</v>
+        <v>2.671051622774015</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -496,7 +566,7 @@
         <v>11</v>
       </c>
       <c r="B22">
-        <v>553</v>
+        <v>598</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
@@ -508,22 +578,22 @@
         <v>12</v>
       </c>
       <c r="F22">
-        <v>529</v>
+        <v>668</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22">
-        <v>2904</v>
+        <v>3738</v>
       </c>
       <c r="I22">
-        <v>-2.277097274652085</v>
+        <v>-2.76965587297382e-8</v>
       </c>
       <c r="J22">
-        <v>-1.7849974656200602</v>
+        <v>-5.2738211951822645e-5</v>
       </c>
       <c r="K22">
-        <v>1.1334157125900748</v>
+        <v>2.2957413056789293</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -531,7 +601,7 @@
         <v>11</v>
       </c>
       <c r="B23">
-        <v>553</v>
+        <v>598</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -543,22 +613,22 @@
         <v>12</v>
       </c>
       <c r="F23">
-        <v>576</v>
+        <v>741</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23">
-        <v>3174</v>
+        <v>4164</v>
       </c>
       <c r="I23">
-        <v>-0.8897682397976558</v>
+        <v>-1.3254037830736253e-8</v>
       </c>
       <c r="J23">
-        <v>-0.7665276727714057</v>
+        <v>-2.3884870119232895e-5</v>
       </c>
       <c r="K23">
-        <v>2.5559471400057454</v>
+        <v>2.124242940248744</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -566,7 +636,7 @@
         <v>11</v>
       </c>
       <c r="B24">
-        <v>553</v>
+        <v>598</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
@@ -578,22 +648,22 @@
         <v>12</v>
       </c>
       <c r="F24">
-        <v>625</v>
+        <v>797</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24">
-        <v>3456</v>
+        <v>4488</v>
       </c>
       <c r="I24">
-        <v>-0.027455219176015493</v>
+        <v>-1.1646552933960439e-8</v>
       </c>
       <c r="J24">
-        <v>-0.026219843639027025</v>
+        <v>-2.311436813657547e-5</v>
       </c>
       <c r="K24">
-        <v>3.5868829109797797</v>
+        <v>2.1298462700937733</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -601,7 +671,7 @@
         <v>11</v>
       </c>
       <c r="B25">
-        <v>553</v>
+        <v>598</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
@@ -613,22 +683,22 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>676</v>
+        <v>861</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25">
-        <v>3750</v>
+        <v>4860</v>
       </c>
       <c r="I25">
-        <v>-0.0010594847444476997</v>
+        <v>-5.999206621650596e-9</v>
       </c>
       <c r="J25">
-        <v>-0.0013854251214837385</v>
+        <v>-1.2677110195593745e-5</v>
       </c>
       <c r="K25">
-        <v>3.057873562430752</v>
+        <v>2.0058532889201794</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -636,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="B26">
-        <v>553</v>
+        <v>598</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -648,22 +718,22 @@
         <v>12</v>
       </c>
       <c r="F26">
-        <v>729</v>
+        <v>927</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26">
-        <v>4056</v>
+        <v>5244</v>
       </c>
       <c r="I26">
-        <v>-0.00043842257872720776</v>
+        <v>-4.499475655726901e-9</v>
       </c>
       <c r="J26">
-        <v>-0.0005397498116947389</v>
+        <v>-9.047063824068058e-6</v>
       </c>
       <c r="K26">
-        <v>2.8560542347379334</v>
+        <v>1.9293622613462942</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -671,7 +741,7 @@
         <v>11</v>
       </c>
       <c r="B27">
-        <v>553</v>
+        <v>598</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -683,22 +753,22 @@
         <v>12</v>
       </c>
       <c r="F27">
-        <v>784</v>
+        <v>977</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27">
-        <v>4374</v>
+        <v>5532</v>
       </c>
       <c r="I27">
-        <v>-0.00021294863043302094</v>
+        <v>-3.984860562384564e-9</v>
       </c>
       <c r="J27">
-        <v>-0.0002516237882071661</v>
+        <v>-8.268211979298931e-6</v>
       </c>
       <c r="K27">
-        <v>2.6901898096229924</v>
+        <v>1.9120709164990701</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -706,7 +776,7 @@
         <v>11</v>
       </c>
       <c r="B28">
-        <v>553</v>
+        <v>598</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -718,22 +788,22 @@
         <v>12</v>
       </c>
       <c r="F28">
-        <v>841</v>
+        <v>1034</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28">
-        <v>4704</v>
+        <v>5862</v>
       </c>
       <c r="I28">
-        <v>-0.00013822425870764344</v>
+        <v>-3.307151174779939e-9</v>
       </c>
       <c r="J28">
-        <v>-0.00017018379770987124</v>
+        <v>-6.829341704893412e-6</v>
       </c>
       <c r="K28">
-        <v>2.609452441333928</v>
+        <v>1.8711865759230855</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -741,7 +811,7 @@
         <v>11</v>
       </c>
       <c r="B29">
-        <v>553</v>
+        <v>598</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -753,22 +823,22 @@
         <v>12</v>
       </c>
       <c r="F29">
-        <v>900</v>
+        <v>1085</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29">
-        <v>5046</v>
+        <v>6156</v>
       </c>
       <c r="I29">
-        <v>-9.76277577408494e-5</v>
+        <v>-3.390311497423336e-9</v>
       </c>
       <c r="J29">
-        <v>-0.00011569204608016185</v>
+        <v>-6.785017803143206e-6</v>
       </c>
       <c r="K29">
-        <v>2.5192270421870173</v>
+        <v>1.8668269688272245</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -776,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="B30">
-        <v>553</v>
+        <v>598</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -788,22 +858,22 @@
         <v>12</v>
       </c>
       <c r="F30">
-        <v>961</v>
+        <v>1177</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30">
-        <v>5400</v>
+        <v>6696</v>
       </c>
       <c r="I30">
-        <v>-7.762656645502136e-5</v>
+        <v>-2.355426015518738e-9</v>
       </c>
       <c r="J30">
-        <v>-9.284933306044178e-5</v>
+        <v>-4.688615716080863e-6</v>
       </c>
       <c r="K30">
-        <v>2.4740804538785834</v>
+        <v>1.7862119956603613</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -811,7 +881,7 @@
         <v>11</v>
       </c>
       <c r="B31">
-        <v>553</v>
+        <v>598</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -823,22 +893,22 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>1024</v>
+        <v>1243</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31">
-        <v>5766</v>
+        <v>7080</v>
       </c>
       <c r="I31">
-        <v>-5.996529924597733e-5</v>
+        <v>-2.037748918447412e-9</v>
       </c>
       <c r="J31">
-        <v>-7.065665643653594e-5</v>
+        <v>-4.228333940018944e-6</v>
       </c>
       <c r="K31">
-        <v>2.409542827802751</v>
+        <v>1.7674162754801386</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -846,7 +916,7 @@
         <v>11</v>
       </c>
       <c r="B32">
-        <v>553</v>
+        <v>598</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -858,22 +928,22 @@
         <v>12</v>
       </c>
       <c r="F32">
-        <v>1089</v>
+        <v>1325</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32">
-        <v>6144</v>
+        <v>7560</v>
       </c>
       <c r="I32">
-        <v>-4.808209608096782e-5</v>
+        <v>-1.7287983101861903e-9</v>
       </c>
       <c r="J32">
-        <v>-5.7514881579325516e-5</v>
+        <v>-3.7112452644150817e-6</v>
       </c>
       <c r="K32">
-        <v>2.3688083672462037</v>
+        <v>1.7422202947352645</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_21.xlsx
+++ b/xls/square_un_16_tri3_21.xlsx
@@ -482,13 +482,13 @@
         <v>2676</v>
       </c>
       <c r="I19">
-        <v>-0.0001374637284752597</v>
+        <v>-2.3319642370370834</v>
       </c>
       <c r="J19">
-        <v>-0.5122504675722445</v>
+        <v>-1.9825197828826597</v>
       </c>
       <c r="K19">
-        <v>2.657847606759506</v>
+        <v>-0.17656038103528765</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -517,13 +517,13 @@
         <v>3138</v>
       </c>
       <c r="I20">
-        <v>-4.4695317076209455e-6</v>
+        <v>-0.8641103529914466</v>
       </c>
       <c r="J20">
-        <v>-0.009564883447708866</v>
+        <v>-0.7596360364946912</v>
       </c>
       <c r="K20">
-        <v>3.2027111743482077</v>
+        <v>2.1130321850344664</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -552,13 +552,13 @@
         <v>3330</v>
       </c>
       <c r="I21">
-        <v>-1.566336761345978e-7</v>
+        <v>-0.3934206025855741</v>
       </c>
       <c r="J21">
-        <v>-0.0003376943310008203</v>
+        <v>-0.34717752712403527</v>
       </c>
       <c r="K21">
-        <v>2.671051622774015</v>
+        <v>2.222082343483225</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -587,13 +587,13 @@
         <v>3738</v>
       </c>
       <c r="I22">
-        <v>-2.76965587297382e-8</v>
+        <v>-8.083840198045157e-5</v>
       </c>
       <c r="J22">
-        <v>-5.2738211951822645e-5</v>
+        <v>-0.00010721423708487325</v>
       </c>
       <c r="K22">
-        <v>2.2957413056789293</v>
+        <v>2.5269770066932065</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -622,13 +622,13 @@
         <v>4164</v>
       </c>
       <c r="I23">
-        <v>-1.3254037830736253e-8</v>
+        <v>-3.168220234778148e-5</v>
       </c>
       <c r="J23">
-        <v>-2.3884870119232895e-5</v>
+        <v>-3.0299847729653455e-5</v>
       </c>
       <c r="K23">
-        <v>2.124242940248744</v>
+        <v>2.184161896520563</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -657,13 +657,13 @@
         <v>4488</v>
       </c>
       <c r="I24">
-        <v>-1.1646552933960439e-8</v>
+        <v>-2.6439985892730476e-5</v>
       </c>
       <c r="J24">
-        <v>-2.311436813657547e-5</v>
+        <v>-2.626747131376443e-5</v>
       </c>
       <c r="K24">
-        <v>2.1298462700937733</v>
+        <v>2.1554798484768094</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -692,13 +692,13 @@
         <v>4860</v>
       </c>
       <c r="I25">
-        <v>-5.999206621650596e-9</v>
+        <v>-1.5171148621073482e-5</v>
       </c>
       <c r="J25">
-        <v>-1.2677110195593745e-5</v>
+        <v>-1.4937220242235275e-5</v>
       </c>
       <c r="K25">
-        <v>2.0058532889201794</v>
+        <v>2.0266564407843517</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -727,13 +727,13 @@
         <v>5244</v>
       </c>
       <c r="I26">
-        <v>-4.499475655726901e-9</v>
+        <v>-8.9233867373509e-6</v>
       </c>
       <c r="J26">
-        <v>-9.047063824068058e-6</v>
+        <v>-9.315173376580853e-6</v>
       </c>
       <c r="K26">
-        <v>1.9293622613462942</v>
+        <v>1.942100271559117</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -762,13 +762,13 @@
         <v>5532</v>
       </c>
       <c r="I27">
-        <v>-3.984860562384564e-9</v>
+        <v>-7.888413642198195e-6</v>
       </c>
       <c r="J27">
-        <v>-8.268211979298931e-6</v>
+        <v>-8.446813684217271e-6</v>
       </c>
       <c r="K27">
-        <v>1.9120709164990701</v>
+        <v>1.9245123898113217</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -797,13 +797,13 @@
         <v>5862</v>
       </c>
       <c r="I28">
-        <v>-3.307151174779939e-9</v>
+        <v>-8.413895328308595e-6</v>
       </c>
       <c r="J28">
-        <v>-6.829341704893412e-6</v>
+        <v>-7.981484630121004e-6</v>
       </c>
       <c r="K28">
-        <v>1.8711865759230855</v>
+        <v>1.8830082125331697</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -832,13 +832,13 @@
         <v>6156</v>
       </c>
       <c r="I29">
-        <v>-3.390311497423336e-9</v>
+        <v>-6.566304823832438e-6</v>
       </c>
       <c r="J29">
-        <v>-6.785017803143206e-6</v>
+        <v>-6.879279989886268e-6</v>
       </c>
       <c r="K29">
-        <v>1.8668269688272245</v>
+        <v>1.879683759664333</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -867,13 +867,13 @@
         <v>6696</v>
       </c>
       <c r="I30">
-        <v>-2.355426015518738e-9</v>
+        <v>-4.483012236101723e-6</v>
       </c>
       <c r="J30">
-        <v>-4.688615716080863e-6</v>
+        <v>-4.725662998632929e-6</v>
       </c>
       <c r="K30">
-        <v>1.7862119956603613</v>
+        <v>1.797475634156088</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -902,13 +902,13 @@
         <v>7080</v>
       </c>
       <c r="I31">
-        <v>-2.037748918447412e-9</v>
+        <v>-4.4320929043697205e-6</v>
       </c>
       <c r="J31">
-        <v>-4.228333940018944e-6</v>
+        <v>-4.487197692644577e-6</v>
       </c>
       <c r="K31">
-        <v>1.7674162754801386</v>
+        <v>1.775462883498225</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -937,13 +937,13 @@
         <v>7560</v>
       </c>
       <c r="I32">
-        <v>-1.7287983101861903e-9</v>
+        <v>-4.156808198590912e-6</v>
       </c>
       <c r="J32">
-        <v>-3.7112452644150817e-6</v>
+        <v>-4.1333316674819385e-6</v>
       </c>
       <c r="K32">
-        <v>1.7422202947352645</v>
+        <v>1.7526692019060022</v>
       </c>
     </row>
   </sheetData>
